--- a/Collections/Kazakhstan/#Kazakhstan#Regular#[1995-present]#circulation_quality.xlsx
+++ b/Collections/Kazakhstan/#Kazakhstan#Regular#[1995-present]#circulation_quality.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\Kazakhstan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5847F5DE-7646-4CF8-9CBC-A991A580C859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F81C484-719D-40DB-A1B1-87F110A9E512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="2280" windowWidth="33150" windowHeight="17700" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2тиын" sheetId="4" r:id="rId1"/>
-    <sheet name="5тиын" sheetId="14" r:id="rId2"/>
-    <sheet name="10тиын" sheetId="15" r:id="rId3"/>
+    <sheet name="10тиын" sheetId="15" r:id="rId2"/>
+    <sheet name="5тиын" sheetId="14" r:id="rId3"/>
     <sheet name="20тиын" sheetId="16" r:id="rId4"/>
     <sheet name="50тиын" sheetId="17" r:id="rId5"/>
     <sheet name="1тенге" sheetId="18" r:id="rId6"/>
@@ -32,7 +32,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'100тенге'!$B$2:$F$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'10тенге'!$B$2:$E$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'10тиын'!$B$2:$E$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'10тиын'!$B$2:$E$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'1тенге'!$B$2:$E$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'200тенге'!$B$2:$F$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'20тенге'!$B$2:$E$2</definedName>
@@ -43,7 +43,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'50тенге'!$B$2:$E$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'50тиын'!$B$2:$E$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'5тенге'!$B$2:$E$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'5тиын'!$B$2:$E$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'5тиын'!$B$2:$E$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -55,6 +55,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -318,7 +321,7 @@
     <author>Пользователь Windows</author>
   </authors>
   <commentList>
-    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{77331229-59EB-467F-B999-7612F3C2B6BA}">
+    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{E23DA8AA-09B4-4DE8-AF7F-0640D0578745}">
       <text>
         <r>
           <rPr>
@@ -334,7 +337,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F2" authorId="0" shapeId="0" xr:uid="{C889E2BD-1B81-46CE-AFDB-CE85EB0CAEFB}">
+    <comment ref="F2" authorId="0" shapeId="0" xr:uid="{D90F7DF7-8653-43AB-9159-63BC0EE45F6E}">
       <text>
         <r>
           <rPr>
@@ -360,7 +363,7 @@
     <author>Пользователь Windows</author>
   </authors>
   <commentList>
-    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{E23DA8AA-09B4-4DE8-AF7F-0640D0578745}">
+    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{77331229-59EB-467F-B999-7612F3C2B6BA}">
       <text>
         <r>
           <rPr>
@@ -376,7 +379,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F2" authorId="0" shapeId="0" xr:uid="{D90F7DF7-8653-43AB-9159-63BC0EE45F6E}">
+    <comment ref="F2" authorId="0" shapeId="0" xr:uid="{C889E2BD-1B81-46CE-AFDB-CE85EB0CAEFB}">
       <text>
         <r>
           <rPr>
@@ -649,7 +652,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2230" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2295" uniqueCount="56">
   <si>
     <t>-</t>
   </si>
@@ -1070,7 +1073,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1136,6 +1139,9 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1152,15 +1158,14 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="172">
+  <dxfs count="179">
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -2514,6 +2519,63 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2535,9 +2597,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="178"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="177" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="176"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -2840,7 +2902,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
@@ -2852,14 +2914,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="24" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="21"/>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="26"/>
+      <c r="D1" s="27"/>
       <c r="E1" s="13" t="s">
         <v>3</v>
       </c>
@@ -2868,7 +2930,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="24"/>
+      <c r="A2" s="25"/>
       <c r="B2" s="22" t="s">
         <v>15</v>
       </c>
@@ -3647,6 +3709,30 @@
       </c>
       <c r="G34" s="10" t="str">
         <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="23">
+        <v>2025</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G35" s="10" t="str">
+        <f t="shared" ref="G35" si="1">IF(OR(AND(F35&gt;1,F35&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -3670,7 +3756,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:F26 F28">
-    <cfRule type="containsText" dxfId="171" priority="61" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="175" priority="61" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3687,7 +3773,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3">
-    <cfRule type="containsText" dxfId="170" priority="47" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="174" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3704,7 +3790,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F32">
-    <cfRule type="containsText" dxfId="169" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="173" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F31))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3721,7 +3807,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F29:F30">
-    <cfRule type="containsText" dxfId="168" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="172" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F29))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3738,11 +3824,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5">
-    <cfRule type="containsText" dxfId="167" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="171" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F5))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F33:F34">
+  <conditionalFormatting sqref="F33:F35">
     <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3754,8 +3840,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F33:F34">
-    <cfRule type="containsText" dxfId="166" priority="19" operator="containsText" text="*-">
+  <conditionalFormatting sqref="F33:F35">
+    <cfRule type="containsText" dxfId="170" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F33))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3772,7 +3858,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="containsText" dxfId="165" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="169" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F6))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3789,7 +3875,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4">
-    <cfRule type="containsText" dxfId="164" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="168" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3806,7 +3892,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F27">
-    <cfRule type="containsText" dxfId="163" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="167" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F27))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3818,7 +3904,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{898A6DD0-372D-42B3-A5A3-53EDFACC0DDB}">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
@@ -3830,14 +3916,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="24" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="21"/>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="26"/>
+      <c r="D1" s="27"/>
       <c r="E1" s="13" t="s">
         <v>3</v>
       </c>
@@ -3846,7 +3932,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="24"/>
+      <c r="A2" s="25"/>
       <c r="B2" s="22" t="s">
         <v>15</v>
       </c>
@@ -4599,6 +4685,30 @@
       </c>
       <c r="G34" s="10" t="str">
         <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="23">
+        <v>2025</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E35" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0</v>
+      </c>
+      <c r="G35" s="10" t="str">
+        <f t="shared" ref="G35" si="2">IF(OR(AND(F35&gt;1,F35&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -4609,6 +4719,40 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <conditionalFormatting sqref="F8:F9 F3 F11 F13 F17:F19">
+    <cfRule type="colorScale" priority="56">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8:F9 F3 F11 F13 F17:F19">
+    <cfRule type="containsText" dxfId="69" priority="55" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F34">
+    <cfRule type="colorScale" priority="50">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F34">
+    <cfRule type="containsText" dxfId="68" priority="49" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F34))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5">
     <cfRule type="colorScale" priority="54">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4620,12 +4764,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F8:F9 F3 F11 F13 F17:F19">
-    <cfRule type="containsText" dxfId="65" priority="53" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F34">
+  <conditionalFormatting sqref="F5">
+    <cfRule type="containsText" dxfId="67" priority="53" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6">
     <cfRule type="colorScale" priority="48">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4637,29 +4781,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F34">
-    <cfRule type="containsText" dxfId="64" priority="47" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F34))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="colorScale" priority="52">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="containsText" dxfId="63" priority="51" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F5))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F6">
+    <cfRule type="containsText" dxfId="66" priority="47" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F6))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4">
     <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4671,12 +4798,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="containsText" dxfId="62" priority="45" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F6))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F4">
+    <cfRule type="containsText" dxfId="65" priority="45" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12">
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12">
+    <cfRule type="containsText" dxfId="64" priority="39" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7">
     <cfRule type="colorScale" priority="44">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4688,12 +4832,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="containsText" dxfId="61" priority="43" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F12">
+  <conditionalFormatting sqref="F7">
+    <cfRule type="containsText" dxfId="63" priority="43" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F7))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F10">
+    <cfRule type="colorScale" priority="42">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F10">
+    <cfRule type="containsText" dxfId="62" priority="41" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F10))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14">
     <cfRule type="colorScale" priority="38">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4705,46 +4866,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F12">
-    <cfRule type="containsText" dxfId="60" priority="37" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F12))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="colorScale" priority="42">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="containsText" dxfId="59" priority="41" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F7))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F10">
-    <cfRule type="colorScale" priority="40">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F10">
-    <cfRule type="containsText" dxfId="58" priority="39" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F10))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F14">
+    <cfRule type="containsText" dxfId="61" priority="37" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F14))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15">
     <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4756,13 +4883,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F14">
-    <cfRule type="containsText" dxfId="57" priority="35" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F14))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F15">
-    <cfRule type="colorScale" priority="34">
+    <cfRule type="containsText" dxfId="60" priority="35" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F33">
+    <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -4773,12 +4900,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F15">
-    <cfRule type="containsText" dxfId="56" priority="33" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F33">
+    <cfRule type="containsText" dxfId="59" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F33))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F16">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4790,12 +4917,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F33">
-    <cfRule type="containsText" dxfId="55" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F33))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F16">
+    <cfRule type="containsText" dxfId="58" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F16))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F20:F31">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4807,12 +4934,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F16">
-    <cfRule type="containsText" dxfId="54" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F16))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F20:F31">
+    <cfRule type="containsText" dxfId="57" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F32">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4824,12 +4951,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F20:F31">
-    <cfRule type="containsText" dxfId="53" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F32">
+    <cfRule type="containsText" dxfId="56" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F32))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F35">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4841,9 +4968,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F32">
-    <cfRule type="containsText" dxfId="52" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F32))))</formula>
+  <conditionalFormatting sqref="F35">
+    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F35))))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4854,7 +4981,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C19897AD-DB32-4802-8079-E69FF40B74A5}">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
@@ -4866,14 +4993,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="24" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="21"/>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="26"/>
+      <c r="D1" s="27"/>
       <c r="E1" s="13" t="s">
         <v>3</v>
       </c>
@@ -4882,7 +5009,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="24"/>
+      <c r="A2" s="25"/>
       <c r="B2" s="22" t="s">
         <v>15</v>
       </c>
@@ -5639,6 +5766,30 @@
       </c>
       <c r="G34" s="10" t="str">
         <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="23">
+        <v>2025</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E35" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0</v>
+      </c>
+      <c r="G35" s="10" t="str">
+        <f t="shared" ref="G35" si="3">IF(OR(AND(F35&gt;1,F35&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -5649,6 +5800,23 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <conditionalFormatting sqref="F8:F9 F3 F11 F13 F17:F19">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8:F9 F3 F11 F13 F17:F19">
+    <cfRule type="containsText" dxfId="55" priority="33" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5">
     <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5660,12 +5828,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F8:F9 F3 F11 F13 F17:F19">
-    <cfRule type="containsText" dxfId="51" priority="31" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F5">
+    <cfRule type="containsText" dxfId="54" priority="31" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F34">
     <cfRule type="colorScale" priority="30">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5677,12 +5845,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="containsText" dxfId="50" priority="29" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F5))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F34">
+    <cfRule type="containsText" dxfId="53" priority="29" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F34))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6">
     <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5694,12 +5862,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F34">
-    <cfRule type="containsText" dxfId="49" priority="27" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F34))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F6">
+    <cfRule type="containsText" dxfId="52" priority="27" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F6))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4">
     <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5711,12 +5879,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="containsText" dxfId="48" priority="25" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F6))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F4">
+    <cfRule type="containsText" dxfId="51" priority="25" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12">
+    <cfRule type="containsText" dxfId="50" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7">
     <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5728,29 +5913,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="containsText" dxfId="47" priority="23" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F12">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F12">
-    <cfRule type="containsText" dxfId="46" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F12))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F7">
+    <cfRule type="containsText" dxfId="49" priority="23" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F7))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F10">
     <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5762,13 +5930,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="containsText" dxfId="45" priority="21" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F7))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F10">
-    <cfRule type="colorScale" priority="20">
+    <cfRule type="containsText" dxfId="48" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F10))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F16">
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -5779,12 +5947,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F10">
-    <cfRule type="containsText" dxfId="44" priority="19" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F10))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F16">
+    <cfRule type="containsText" dxfId="47" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F16))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F33">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F33">
+    <cfRule type="containsText" dxfId="46" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F33))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F20:F32">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5796,13 +5981,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F16">
-    <cfRule type="containsText" dxfId="43" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F16))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F33">
-    <cfRule type="colorScale" priority="12">
+  <conditionalFormatting sqref="F20:F32">
+    <cfRule type="containsText" dxfId="45" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -5813,13 +5998,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F33">
-    <cfRule type="containsText" dxfId="42" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F33))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F20:F32">
-    <cfRule type="colorScale" priority="8">
+  <conditionalFormatting sqref="F14">
+    <cfRule type="containsText" dxfId="44" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F14))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -5830,12 +6015,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F20:F32">
-    <cfRule type="containsText" dxfId="41" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F14">
+  <conditionalFormatting sqref="F15">
+    <cfRule type="containsText" dxfId="43" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F35">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5847,26 +6032,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F14">
-    <cfRule type="containsText" dxfId="40" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F14))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F15">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F15">
-    <cfRule type="containsText" dxfId="39" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F15))))</formula>
+  <conditionalFormatting sqref="F35">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F35))))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5877,7 +6045,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEF9BCBB-C212-4D6D-A2A3-BA20330D3629}">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
@@ -5889,14 +6057,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="24" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="21"/>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="26"/>
+      <c r="D1" s="27"/>
       <c r="E1" s="13" t="s">
         <v>3</v>
       </c>
@@ -5905,7 +6073,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="24"/>
+      <c r="A2" s="25"/>
       <c r="B2" s="22" t="s">
         <v>15</v>
       </c>
@@ -6670,6 +6838,30 @@
       </c>
       <c r="G34" s="10" t="str">
         <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="23">
+        <v>2025</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E35" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0</v>
+      </c>
+      <c r="G35" s="10" t="str">
+        <f t="shared" ref="G35" si="5">IF(OR(AND(F35&gt;1,F35&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -6680,6 +6872,23 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <conditionalFormatting sqref="F8:F9 F11 F13 F18:F24">
+    <cfRule type="colorScale" priority="44">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8:F9 F11 F13 F18:F24">
+    <cfRule type="containsText" dxfId="42" priority="43" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F8))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5">
     <cfRule type="colorScale" priority="42">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6691,12 +6900,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F8:F9 F11 F13 F18:F24">
-    <cfRule type="containsText" dxfId="38" priority="41" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F8))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F5">
+    <cfRule type="containsText" dxfId="41" priority="41" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F34">
     <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6708,12 +6917,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="containsText" dxfId="37" priority="39" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F5))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F34">
+    <cfRule type="containsText" dxfId="40" priority="39" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F34))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6">
     <cfRule type="colorScale" priority="38">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6725,12 +6934,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F34">
-    <cfRule type="containsText" dxfId="36" priority="37" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F34))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F6">
+    <cfRule type="containsText" dxfId="39" priority="37" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F6))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4">
     <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6742,12 +6951,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="containsText" dxfId="35" priority="35" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F6))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F4">
+    <cfRule type="containsText" dxfId="38" priority="35" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F33">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F33">
+    <cfRule type="containsText" dxfId="37" priority="27" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F33))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7">
     <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6759,12 +6985,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="containsText" dxfId="34" priority="33" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F33">
+  <conditionalFormatting sqref="F7">
+    <cfRule type="containsText" dxfId="36" priority="33" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F7))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F16">
     <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6776,29 +7002,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F33">
-    <cfRule type="containsText" dxfId="33" priority="25" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F33))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="colorScale" priority="32">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="containsText" dxfId="32" priority="31" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F7))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F16">
+    <cfRule type="containsText" dxfId="35" priority="25" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F16))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F29:F32">
     <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6810,12 +7019,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F16">
-    <cfRule type="containsText" dxfId="31" priority="23" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F16))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F29:F32">
+    <cfRule type="containsText" dxfId="34" priority="23" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15">
     <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6827,12 +7036,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F29:F32">
-    <cfRule type="containsText" dxfId="30" priority="21" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F29))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F15">
+    <cfRule type="containsText" dxfId="33" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14">
     <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6844,12 +7053,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F15">
-    <cfRule type="containsText" dxfId="29" priority="19" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F14">
+    <cfRule type="containsText" dxfId="32" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F14))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6861,12 +7070,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F14">
-    <cfRule type="containsText" dxfId="28" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F14))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F3">
+    <cfRule type="containsText" dxfId="31" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12">
+    <cfRule type="containsText" dxfId="30" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F17">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6878,17 +7092,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3">
-    <cfRule type="containsText" dxfId="27" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F12">
-    <cfRule type="containsText" dxfId="26" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F12))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F17">
+    <cfRule type="containsText" dxfId="29" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F17))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6900,12 +7109,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F17">
-    <cfRule type="containsText" dxfId="25" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F17))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F25">
+    <cfRule type="containsText" dxfId="28" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F26">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6917,12 +7126,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F25">
-    <cfRule type="containsText" dxfId="24" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F26">
+    <cfRule type="containsText" dxfId="27" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F26))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F27">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6934,12 +7143,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F26">
-    <cfRule type="containsText" dxfId="23" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F26))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F27">
+    <cfRule type="containsText" dxfId="26" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F27))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F28">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6951,12 +7160,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F27">
-    <cfRule type="containsText" dxfId="22" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F27))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F28">
+    <cfRule type="containsText" dxfId="25" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F28))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F10">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6968,12 +7177,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F28">
-    <cfRule type="containsText" dxfId="21" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F28))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F10">
+    <cfRule type="containsText" dxfId="24" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F10))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6985,12 +7194,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F10">
-    <cfRule type="containsText" dxfId="20" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F10))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F12">
+  <conditionalFormatting sqref="F35">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -7002,6 +7206,11 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F35">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F35))))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -7010,7 +7219,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F9C7DAA-01C4-4861-B3EA-F5AF89B42AE1}">
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
@@ -7022,14 +7231,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="24" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="21"/>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="26"/>
+      <c r="D1" s="27"/>
       <c r="E1" s="20"/>
       <c r="F1" s="13" t="s">
         <v>3</v>
@@ -7039,7 +7248,7 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="24"/>
+      <c r="A2" s="25"/>
       <c r="B2" s="22" t="s">
         <v>15</v>
       </c>
@@ -7857,6 +8066,33 @@
       </c>
       <c r="H34" s="10" t="str">
         <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="23">
+        <v>2025</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="F35" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="G35" s="2">
+        <v>0</v>
+      </c>
+      <c r="H35" s="10" t="str">
+        <f t="shared" ref="H35" si="4">IF(OR(AND(G35&gt;1,G35&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -7867,7 +8103,7 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <conditionalFormatting sqref="G5:G11 G13 G18:G28">
-    <cfRule type="colorScale" priority="52">
+    <cfRule type="colorScale" priority="54">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -7879,12 +8115,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G13 G5:G11 G18:G28">
-    <cfRule type="containsText" dxfId="19" priority="51" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="23" priority="53" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G5))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G34">
-    <cfRule type="colorScale" priority="48">
+    <cfRule type="colorScale" priority="50">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -7896,12 +8132,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G34">
-    <cfRule type="containsText" dxfId="18" priority="47" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="22" priority="49" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G34))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4">
-    <cfRule type="colorScale" priority="44">
+    <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -7913,12 +8149,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4">
-    <cfRule type="containsText" dxfId="17" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="21" priority="45" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3">
-    <cfRule type="colorScale" priority="30">
+    <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -7930,11 +8166,96 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3">
-    <cfRule type="containsText" dxfId="16" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="20" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G14">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G14">
+    <cfRule type="containsText" dxfId="19" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G14))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G16">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G16">
+    <cfRule type="containsText" dxfId="18" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G16))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G12">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G12">
+    <cfRule type="containsText" dxfId="17" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G17">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G17">
+    <cfRule type="containsText" dxfId="16" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G17))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G29:G33">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G29:G33">
+    <cfRule type="containsText" dxfId="15" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G15">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -7946,80 +8267,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G14">
-    <cfRule type="containsText" dxfId="15" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G14))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G16">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G16">
-    <cfRule type="containsText" dxfId="14" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G16))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G12">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G12">
-    <cfRule type="containsText" dxfId="13" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G12))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G17">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G17">
-    <cfRule type="containsText" dxfId="12" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G17))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G29:G33">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G29:G33">
-    <cfRule type="containsText" dxfId="11" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G29))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G15">
+    <cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G35">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -8031,9 +8284,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G15">
-    <cfRule type="containsText" dxfId="10" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G15))))</formula>
+  <conditionalFormatting sqref="G35">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G35))))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8044,7 +8297,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9959059-BCFD-46F3-922E-B2B85AC54E97}">
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
@@ -8056,14 +8309,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="24" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="21"/>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="26"/>
+      <c r="D1" s="27"/>
       <c r="E1" s="20"/>
       <c r="F1" s="13" t="s">
         <v>3</v>
@@ -8073,7 +8326,7 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="24"/>
+      <c r="A2" s="25"/>
       <c r="B2" s="22" t="s">
         <v>15</v>
       </c>
@@ -8897,6 +9150,31 @@
       </c>
       <c r="H34" s="10" t="str">
         <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="23">
+        <v>2025</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="H35" s="10" t="str">
+        <f t="shared" ref="H35" si="4">IF(OR(AND(G35&gt;1,G35&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -8907,6 +9185,23 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <conditionalFormatting sqref="G5:G28">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5:G28">
+    <cfRule type="containsText" dxfId="13" priority="25" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G34">
     <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -8918,12 +9213,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:G28">
-    <cfRule type="containsText" dxfId="9" priority="23" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G5))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G34">
+    <cfRule type="containsText" dxfId="12" priority="23" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G34))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4">
     <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -8935,12 +9230,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G34">
-    <cfRule type="containsText" dxfId="8" priority="21" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G34))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G4">
+    <cfRule type="containsText" dxfId="11" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
     <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -8952,13 +9247,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4">
-    <cfRule type="containsText" dxfId="7" priority="19" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G3">
-    <cfRule type="colorScale" priority="18">
+    <cfRule type="containsText" dxfId="10" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G30:G31 G33">
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -8969,13 +9264,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
-    <cfRule type="containsText" dxfId="6" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G30:G31 G33">
-    <cfRule type="colorScale" priority="10">
+    <cfRule type="containsText" dxfId="9" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G30))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G29">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -8986,12 +9281,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G30:G31 G33">
-    <cfRule type="containsText" dxfId="5" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G30))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G29">
+    <cfRule type="containsText" dxfId="8" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G32">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -9003,12 +9298,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G29">
-    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G29))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G32">
+    <cfRule type="containsText" dxfId="7" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G32))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G35">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -9020,9 +9315,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G32">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G32))))</formula>
+  <conditionalFormatting sqref="G35">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G35))))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9122,8 +9417,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC84B87D-4EE2-489E-97AB-ED45BA8253B3}">
-  <dimension ref="A1:H34"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E179BEC1-8C55-4CDE-9190-5B00D1609C48}">
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
@@ -9135,23 +9430,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="24" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="21"/>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="26"/>
+      <c r="D1" s="27"/>
       <c r="E1" s="13" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="24"/>
+      <c r="A2" s="25"/>
       <c r="B2" s="22" t="s">
         <v>15</v>
       </c>
@@ -9181,7 +9476,7 @@
         <v>4</v>
       </c>
       <c r="F3" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="10" t="str">
         <f t="shared" ref="G3:G34" si="0">IF(OR(AND(F3&gt;1,F3&lt;&gt;"-")),"Can exchange","")</f>
@@ -9933,980 +10228,27 @@
         <v/>
       </c>
     </row>
-  </sheetData>
-  <autoFilter ref="B2:E2" xr:uid="{FC84B87D-4EE2-489E-97AB-ED45BA8253B3}"/>
-  <mergeCells count="2">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:D1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="F7:F26 F28">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7:F26 F28">
-    <cfRule type="containsText" dxfId="162" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F7))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3">
-    <cfRule type="containsText" dxfId="161" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F31:F32">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F31:F32">
-    <cfRule type="containsText" dxfId="160" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F31))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F29:F30">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F29:F30">
-    <cfRule type="containsText" dxfId="159" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F29))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="containsText" dxfId="158" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F5))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F33:F34">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F33:F34">
-    <cfRule type="containsText" dxfId="157" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F33))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="containsText" dxfId="156" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F6))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="containsText" dxfId="155" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F27">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F27">
-    <cfRule type="containsText" dxfId="154" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F27))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E179BEC1-8C55-4CDE-9190-5B00D1609C48}">
-  <dimension ref="A1:H34"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="5.6328125" customWidth="1"/>
-    <col min="2" max="2" width="50.6328125" style="3" customWidth="1"/>
-    <col min="3" max="4" width="33.6328125" customWidth="1"/>
-    <col min="5" max="5" width="12.6328125" customWidth="1"/>
-    <col min="6" max="6" width="3.6328125" customWidth="1"/>
-    <col min="7" max="7" width="12.6328125" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="26"/>
-      <c r="E1" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="24"/>
-      <c r="B2" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="15">
-        <v>1993</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="2">
-        <v>1</v>
-      </c>
-      <c r="G3" s="10" t="str">
-        <f t="shared" ref="G3:G34" si="0">IF(OR(AND(F3&gt;1,F3&lt;&gt;"-")),"Can exchange","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="15">
-        <v>1994</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G4" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="15">
-        <v>1995</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G5" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="15">
-        <v>1996</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G6" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="15">
-        <v>1997</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G7" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H7" s="4"/>
-    </row>
-    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="15">
-        <v>1998</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G8" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="15">
-        <v>1999</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G9" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="15">
-        <v>2000</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G10" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="15">
-        <v>2001</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G11" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="15">
-        <v>2002</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G12" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="15">
-        <v>2003</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G13" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="15">
-        <v>2004</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G14" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="15">
-        <v>2005</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G15" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="15">
-        <v>2006</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G16" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="15">
-        <v>2007</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G17" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="15">
-        <v>2008</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G18" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="15">
-        <v>2009</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G19" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="15">
-        <v>2010</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G20" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="15">
-        <v>2011</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G21" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="15">
-        <v>2012</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G22" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="15">
-        <v>2013</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G23" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="15">
-        <v>2014</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G24" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="15">
-        <v>2015</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G25" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="15">
-        <v>2016</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G26" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="15">
-        <v>2017</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G27" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="15">
-        <v>2018</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E28" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G28" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="15">
-        <v>2019</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G29" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="15">
-        <v>2020</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E30" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G30" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="15">
-        <v>2021</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E31" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G31" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="15">
-        <v>2022</v>
-      </c>
-      <c r="B32" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E32" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G32" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="15">
-        <v>2023</v>
-      </c>
-      <c r="B33" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E33" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G33" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="15">
-        <v>2024</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C34" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E34" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G34" s="10" t="str">
-        <f t="shared" si="0"/>
+    <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="23">
+        <v>2025</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G35" s="10" t="str">
+        <f t="shared" ref="G35" si="1">IF(OR(AND(F35&gt;1,F35&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -10929,7 +10271,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:F26 F28">
-    <cfRule type="containsText" dxfId="153" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="166" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10946,11 +10288,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3">
-    <cfRule type="containsText" dxfId="152" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="165" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F31:F32">
+  <conditionalFormatting sqref="F31:F32 F35">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -10962,8 +10304,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F31:F32">
-    <cfRule type="containsText" dxfId="151" priority="9" operator="containsText" text="*-">
+  <conditionalFormatting sqref="F31:F32 F35">
+    <cfRule type="containsText" dxfId="164" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F31))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10980,7 +10322,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F29:F30">
-    <cfRule type="containsText" dxfId="150" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="163" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F29))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10997,7 +10339,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5">
-    <cfRule type="containsText" dxfId="149" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="162" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11014,7 +10356,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F33:F34">
-    <cfRule type="containsText" dxfId="148" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="161" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F33))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11031,7 +10373,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="containsText" dxfId="147" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="160" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F6))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11048,7 +10390,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4">
-    <cfRule type="containsText" dxfId="146" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="159" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11065,7 +10407,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F27">
-    <cfRule type="containsText" dxfId="145" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="158" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F27))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11075,9 +10417,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B613366D-3DF2-4C8B-833D-DFFD341C6695}">
-  <dimension ref="A1:H34"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC84B87D-4EE2-489E-97AB-ED45BA8253B3}">
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
@@ -11089,23 +10431,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="24" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="21"/>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="26"/>
+      <c r="D1" s="27"/>
       <c r="E1" s="13" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="24"/>
+      <c r="A2" s="25"/>
       <c r="B2" s="22" t="s">
         <v>15</v>
       </c>
@@ -11135,7 +10477,7 @@
         <v>4</v>
       </c>
       <c r="F3" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="10" t="str">
         <f t="shared" ref="G3:G34" si="0">IF(OR(AND(F3&gt;1,F3&lt;&gt;"-")),"Can exchange","")</f>
@@ -11884,6 +11226,1031 @@
       </c>
       <c r="G34" s="10" t="str">
         <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="23">
+        <v>2025</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G35" s="10" t="str">
+        <f t="shared" ref="G35" si="1">IF(OR(AND(F35&gt;1,F35&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="B2:E2" xr:uid="{FC84B87D-4EE2-489E-97AB-ED45BA8253B3}"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:D1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="F7:F26 F28 F35">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7:F26 F28 F35">
+    <cfRule type="containsText" dxfId="157" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F7))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3">
+    <cfRule type="containsText" dxfId="156" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F31:F32">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F31:F32">
+    <cfRule type="containsText" dxfId="155" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F31))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F29:F30">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F29:F30">
+    <cfRule type="containsText" dxfId="154" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5">
+    <cfRule type="containsText" dxfId="153" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F33:F34">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F33:F34">
+    <cfRule type="containsText" dxfId="152" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F33))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6">
+    <cfRule type="containsText" dxfId="151" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F6))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4">
+    <cfRule type="containsText" dxfId="150" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F27">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F27">
+    <cfRule type="containsText" dxfId="149" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F27))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B613366D-3DF2-4C8B-833D-DFFD341C6695}">
+  <dimension ref="A1:H35"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="5.6328125" customWidth="1"/>
+    <col min="2" max="2" width="50.6328125" style="3" customWidth="1"/>
+    <col min="3" max="4" width="33.6328125" customWidth="1"/>
+    <col min="5" max="5" width="12.6328125" customWidth="1"/>
+    <col min="6" max="6" width="3.6328125" customWidth="1"/>
+    <col min="7" max="7" width="12.6328125" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="27"/>
+      <c r="E1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="25"/>
+      <c r="B2" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="15">
+        <v>1993</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1</v>
+      </c>
+      <c r="G3" s="10" t="str">
+        <f t="shared" ref="G3:G33" si="0">IF(OR(AND(F3&gt;1,F3&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="15">
+        <v>1994</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="15">
+        <v>1995</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G5" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="15">
+        <v>1996</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G6" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="15">
+        <v>1997</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G7" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H7" s="4"/>
+    </row>
+    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="15">
+        <v>1998</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G8" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="15">
+        <v>1999</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G9" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="15">
+        <v>2000</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G10" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="15">
+        <v>2001</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G11" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="15">
+        <v>2002</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G12" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="15">
+        <v>2003</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G13" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="15">
+        <v>2004</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G14" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="15">
+        <v>2005</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G15" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="15">
+        <v>2006</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G16" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="15">
+        <v>2007</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G17" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="15">
+        <v>2008</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G18" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="15">
+        <v>2009</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G19" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="15">
+        <v>2010</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G20" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="15">
+        <v>2011</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G21" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="15">
+        <v>2012</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G22" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="15">
+        <v>2013</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G23" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="15">
+        <v>2014</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G24" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="15">
+        <v>2015</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G25" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="15">
+        <v>2016</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G26" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="15">
+        <v>2017</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G27" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="15">
+        <v>2018</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G28" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="15">
+        <v>2019</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G29" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="15">
+        <v>2020</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G30" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="15">
+        <v>2021</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G31" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="15">
+        <v>2022</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G32" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="15">
+        <v>2023</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G33" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="23">
+        <v>2024</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G34" s="10" t="str">
+        <f t="shared" ref="G34:G35" si="1">IF(OR(AND(F34&gt;1,F34&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="23">
+        <v>2025</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G35" s="10" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -11906,7 +12273,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:F26 F28">
-    <cfRule type="containsText" dxfId="144" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="148" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11923,11 +12290,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3">
-    <cfRule type="containsText" dxfId="143" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="147" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F31:F32">
+  <conditionalFormatting sqref="F31:F32 F35">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -11939,12 +12306,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F31:F32">
-    <cfRule type="containsText" dxfId="142" priority="9" operator="containsText" text="*-">
+  <conditionalFormatting sqref="F31:F32 F35">
+    <cfRule type="containsText" dxfId="146" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F31))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F29:F30">
+  <conditionalFormatting sqref="F29:F30 F34">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -11956,8 +12323,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F29:F30">
-    <cfRule type="containsText" dxfId="141" priority="11" operator="containsText" text="*-">
+  <conditionalFormatting sqref="F29:F30 F34">
+    <cfRule type="containsText" dxfId="145" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F29))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11974,11 +12341,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5">
-    <cfRule type="containsText" dxfId="140" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="144" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F5))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F33:F34">
+  <conditionalFormatting sqref="F33">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -11990,8 +12357,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F33:F34">
-    <cfRule type="containsText" dxfId="139" priority="7" operator="containsText" text="*-">
+  <conditionalFormatting sqref="F33">
+    <cfRule type="containsText" dxfId="143" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F33))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12008,7 +12375,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="containsText" dxfId="138" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="142" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F6))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12025,7 +12392,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4">
-    <cfRule type="containsText" dxfId="137" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="141" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12042,7 +12409,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F27">
-    <cfRule type="containsText" dxfId="136" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="140" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F27))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12054,7 +12421,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28ED3FA8-A963-416C-AC0D-D2266577F95E}">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
@@ -12066,14 +12433,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="24" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="21"/>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="26"/>
+      <c r="D1" s="27"/>
       <c r="E1" s="13" t="s">
         <v>3</v>
       </c>
@@ -12082,7 +12449,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="24"/>
+      <c r="A2" s="25"/>
       <c r="B2" s="22" t="s">
         <v>15</v>
       </c>
@@ -12861,6 +13228,30 @@
       </c>
       <c r="G34" s="10" t="str">
         <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="23">
+        <v>2025</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G35" s="10" t="str">
+        <f t="shared" ref="G35" si="1">IF(OR(AND(F35&gt;1,F35&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -12883,7 +13274,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:F26 F28">
-    <cfRule type="containsText" dxfId="135" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="139" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12900,7 +13291,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3">
-    <cfRule type="containsText" dxfId="134" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="138" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12917,7 +13308,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F32">
-    <cfRule type="containsText" dxfId="133" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="137" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F31))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12934,7 +13325,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F29:F30">
-    <cfRule type="containsText" dxfId="132" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="136" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F29))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12951,11 +13342,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5">
-    <cfRule type="containsText" dxfId="131" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="135" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F5))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F33:F34">
+  <conditionalFormatting sqref="F33:F35">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -12967,8 +13358,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F33:F34">
-    <cfRule type="containsText" dxfId="130" priority="7" operator="containsText" text="*-">
+  <conditionalFormatting sqref="F33:F35">
+    <cfRule type="containsText" dxfId="134" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F33))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12985,7 +13376,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="containsText" dxfId="129" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="133" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F6))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13002,7 +13393,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4">
-    <cfRule type="containsText" dxfId="128" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="132" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13019,7 +13410,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F27">
-    <cfRule type="containsText" dxfId="127" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="131" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F27))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13031,7 +13422,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60F10BB6-3A9D-4F47-ADD6-C0193E61F9C7}">
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
@@ -13043,14 +13434,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="24" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="21"/>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="26"/>
+      <c r="D1" s="27"/>
       <c r="E1" s="13" t="s">
         <v>3</v>
       </c>
@@ -13059,7 +13450,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="24"/>
+      <c r="A2" s="25"/>
       <c r="B2" s="22" t="s">
         <v>15</v>
       </c>
@@ -13880,6 +14271,30 @@
       </c>
       <c r="G37" s="10" t="str">
         <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="23">
+        <v>2025</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E38" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0</v>
+      </c>
+      <c r="G38" s="10" t="str">
+        <f t="shared" ref="G38" si="9">IF(OR(AND(F38&gt;1,F38&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -13890,7 +14305,7 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <conditionalFormatting sqref="F8:F9 F3 F11 F13 F16:F20">
-    <cfRule type="colorScale" priority="58">
+    <cfRule type="colorScale" priority="60">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -13902,11 +14317,62 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8:F9 F3 F11 F13 F16:F20">
-    <cfRule type="containsText" dxfId="126" priority="57" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="130" priority="59" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F35">
+    <cfRule type="colorScale" priority="52">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F35">
+    <cfRule type="containsText" dxfId="129" priority="51" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F35))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6">
+    <cfRule type="colorScale" priority="48">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6">
+    <cfRule type="containsText" dxfId="128" priority="47" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F6))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5">
+    <cfRule type="colorScale" priority="56">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5">
+    <cfRule type="containsText" dxfId="127" priority="55" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F37">
     <cfRule type="colorScale" priority="50">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -13918,12 +14384,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F35">
-    <cfRule type="containsText" dxfId="125" priority="49" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F35))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
+  <conditionalFormatting sqref="F37">
+    <cfRule type="containsText" dxfId="126" priority="49" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F37))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4">
     <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -13935,13 +14401,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="containsText" dxfId="124" priority="45" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F6))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="colorScale" priority="54">
+  <conditionalFormatting sqref="F4">
+    <cfRule type="containsText" dxfId="125" priority="45" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12">
+    <cfRule type="colorScale" priority="38">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -13952,13 +14418,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="containsText" dxfId="123" priority="53" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F5))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F37">
-    <cfRule type="colorScale" priority="48">
+  <conditionalFormatting sqref="F12">
+    <cfRule type="containsText" dxfId="124" priority="37" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7">
+    <cfRule type="colorScale" priority="42">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -13969,13 +14435,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F37">
-    <cfRule type="containsText" dxfId="122" priority="47" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F37))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="colorScale" priority="44">
+  <conditionalFormatting sqref="F7">
+    <cfRule type="containsText" dxfId="123" priority="41" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F7))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F10">
+    <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -13986,12 +14452,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="containsText" dxfId="121" priority="43" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F12">
+  <conditionalFormatting sqref="F10">
+    <cfRule type="containsText" dxfId="122" priority="39" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F10))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F27">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F27">
+    <cfRule type="containsText" dxfId="121" priority="23" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F27))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14">
     <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -14003,13 +14486,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F12">
+  <conditionalFormatting sqref="F14">
     <cfRule type="containsText" dxfId="120" priority="35" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F12))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="colorScale" priority="40">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F14))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15">
+    <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -14020,13 +14503,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="containsText" dxfId="119" priority="39" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F7))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F10">
-    <cfRule type="colorScale" priority="38">
+  <conditionalFormatting sqref="F15">
+    <cfRule type="containsText" dxfId="119" priority="33" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F21">
+    <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -14037,12 +14520,63 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F10">
-    <cfRule type="containsText" dxfId="118" priority="37" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F10))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F27">
+  <conditionalFormatting sqref="F21">
+    <cfRule type="containsText" dxfId="118" priority="31" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22">
+    <cfRule type="containsText" dxfId="117" priority="29" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F22))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23">
+    <cfRule type="containsText" dxfId="116" priority="27" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F23))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25">
+    <cfRule type="containsText" dxfId="115" priority="25" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F29">
     <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -14054,114 +14588,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F27">
-    <cfRule type="containsText" dxfId="117" priority="21" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F27))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F14">
-    <cfRule type="colorScale" priority="34">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F14">
-    <cfRule type="containsText" dxfId="116" priority="33" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F14))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F15">
-    <cfRule type="colorScale" priority="32">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F15">
-    <cfRule type="containsText" dxfId="115" priority="31" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F21">
-    <cfRule type="colorScale" priority="30">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F21">
-    <cfRule type="containsText" dxfId="114" priority="29" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F22">
-    <cfRule type="colorScale" priority="28">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F22">
-    <cfRule type="containsText" dxfId="113" priority="27" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F22))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F23">
-    <cfRule type="colorScale" priority="26">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F23">
-    <cfRule type="containsText" dxfId="112" priority="25" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F23))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F25">
-    <cfRule type="colorScale" priority="24">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F25">
-    <cfRule type="containsText" dxfId="111" priority="23" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F29">
+    <cfRule type="containsText" dxfId="114" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F30">
     <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -14173,12 +14605,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F29">
-    <cfRule type="containsText" dxfId="110" priority="19" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F29))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F30">
+    <cfRule type="containsText" dxfId="113" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F30))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F31">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -14190,12 +14622,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F30">
-    <cfRule type="containsText" dxfId="109" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F30))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F31">
+    <cfRule type="containsText" dxfId="112" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F31))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F24">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -14207,12 +14639,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F31">
-    <cfRule type="containsText" dxfId="108" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F31))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F24">
+    <cfRule type="containsText" dxfId="111" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F24))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F26">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -14224,12 +14656,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F24">
-    <cfRule type="containsText" dxfId="107" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F24))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F26">
+    <cfRule type="containsText" dxfId="110" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F26))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F28">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -14241,12 +14673,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F26">
-    <cfRule type="containsText" dxfId="106" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F26))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F28">
+    <cfRule type="containsText" dxfId="109" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F28))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F32">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -14258,12 +14690,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F28">
-    <cfRule type="containsText" dxfId="105" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F28))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F32">
+    <cfRule type="containsText" dxfId="108" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F32))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F33">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -14275,12 +14707,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F32">
-    <cfRule type="containsText" dxfId="104" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F32))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F33">
+    <cfRule type="containsText" dxfId="107" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F33))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F34">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -14292,12 +14724,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F33">
-    <cfRule type="containsText" dxfId="103" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F33))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F34">
+    <cfRule type="containsText" dxfId="106" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F34))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F36">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -14309,12 +14741,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F34">
-    <cfRule type="containsText" dxfId="102" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F34))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F36">
+    <cfRule type="containsText" dxfId="105" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F36))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F38">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -14326,9 +14758,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F36">
-    <cfRule type="containsText" dxfId="101" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F36))))</formula>
+  <conditionalFormatting sqref="F38">
+    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F38))))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14339,7 +14771,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C0252CA-5787-40F6-97A3-51258DB4FC20}">
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
@@ -14351,14 +14783,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="24" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="21"/>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="26"/>
+      <c r="D1" s="27"/>
       <c r="E1" s="13" t="s">
         <v>3</v>
       </c>
@@ -14367,7 +14799,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="24"/>
+      <c r="A2" s="25"/>
       <c r="B2" s="22" t="s">
         <v>15</v>
       </c>
@@ -15218,6 +15650,30 @@
       </c>
       <c r="G37" s="10" t="str">
         <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="23">
+        <v>2025</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G38" s="10" t="str">
+        <f t="shared" ref="G38" si="5">IF(OR(AND(F38&gt;1,F38&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -15227,7 +15683,7 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:D1"/>
   </mergeCells>
-  <conditionalFormatting sqref="F17:F33 F35 F37">
+  <conditionalFormatting sqref="F17:F33 F35 F37:F38">
     <cfRule type="colorScale" priority="60">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -15239,8 +15695,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F17:F33 F35 F37">
-    <cfRule type="containsText" dxfId="100" priority="59" operator="containsText" text="*-">
+  <conditionalFormatting sqref="F17:F33 F35 F37:F38">
+    <cfRule type="containsText" dxfId="104" priority="59" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F17))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15257,7 +15713,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15">
-    <cfRule type="containsText" dxfId="99" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="103" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F15))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15274,7 +15730,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16">
-    <cfRule type="containsText" dxfId="98" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="102" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F16))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15291,7 +15747,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F14">
-    <cfRule type="containsText" dxfId="97" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="101" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15308,7 +15764,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F34">
-    <cfRule type="containsText" dxfId="96" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="100" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F34))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15325,7 +15781,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F36">
-    <cfRule type="containsText" dxfId="95" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="99" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F36))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15337,7 +15793,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8262B2A2-C0EC-40CD-9383-19C163C4D032}">
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
@@ -15349,14 +15805,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="24" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="21"/>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="26"/>
+      <c r="D1" s="27"/>
       <c r="E1" s="13" t="s">
         <v>3</v>
       </c>
@@ -15365,7 +15821,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="24"/>
+      <c r="A2" s="25"/>
       <c r="B2" s="22" t="s">
         <v>15</v>
       </c>
@@ -15424,7 +15880,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="10" t="str">
-        <f t="shared" ref="G4:G37" si="1">IF(OR(AND(F4&gt;1,F4&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="G4:G38" si="1">IF(OR(AND(F4&gt;1,F4&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -16217,6 +16673,30 @@
         <v>0</v>
       </c>
       <c r="G37" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="23">
+        <v>2025</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G38" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -16227,7 +16707,7 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:D1"/>
   </mergeCells>
-  <conditionalFormatting sqref="F12:F37">
+  <conditionalFormatting sqref="F12:F38">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -16239,8 +16719,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F12:F37">
-    <cfRule type="containsText" dxfId="94" priority="13" operator="containsText" text="*-">
+  <conditionalFormatting sqref="F12:F38">
+    <cfRule type="containsText" dxfId="98" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16257,7 +16737,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F11">
-    <cfRule type="containsText" dxfId="93" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="97" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16274,7 +16754,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3">
-    <cfRule type="containsText" dxfId="92" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="96" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16286,7 +16766,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA6C094A-BCA9-47D9-8131-35A8E9CCEDE1}">
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
@@ -16298,14 +16778,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="24" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="21"/>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="26"/>
+      <c r="D1" s="27"/>
       <c r="E1" s="13" t="s">
         <v>3</v>
       </c>
@@ -16314,7 +16794,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="24"/>
+      <c r="A2" s="25"/>
       <c r="B2" s="22" t="s">
         <v>15</v>
       </c>
@@ -17087,6 +17567,30 @@
       </c>
       <c r="G35" s="10" t="str">
         <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="23">
+        <v>2025</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E36" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0</v>
+      </c>
+      <c r="G36" s="10" t="str">
+        <f t="shared" ref="G36" si="3">IF(OR(AND(F36&gt;1,F36&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -17097,6 +17601,40 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <conditionalFormatting sqref="F8:F9 F3 F11 F13 F17:F19">
+    <cfRule type="colorScale" priority="58">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8:F9 F3 F11 F13 F17:F19">
+    <cfRule type="containsText" dxfId="95" priority="57" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F33">
+    <cfRule type="colorScale" priority="54">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F33">
+    <cfRule type="containsText" dxfId="94" priority="53" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F33))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5">
     <cfRule type="colorScale" priority="56">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17108,12 +17646,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F8:F9 F3 F11 F13 F17:F19">
-    <cfRule type="containsText" dxfId="91" priority="55" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F33">
+  <conditionalFormatting sqref="F5">
+    <cfRule type="containsText" dxfId="93" priority="55" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F35">
     <cfRule type="colorScale" priority="52">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17125,29 +17663,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F33">
-    <cfRule type="containsText" dxfId="90" priority="51" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F33))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="colorScale" priority="54">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="containsText" dxfId="89" priority="53" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F5))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F35">
+    <cfRule type="containsText" dxfId="92" priority="51" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F35))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6">
     <cfRule type="colorScale" priority="50">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17159,12 +17680,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F35">
-    <cfRule type="containsText" dxfId="88" priority="49" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F35))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F6">
+    <cfRule type="containsText" dxfId="91" priority="49" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F6))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4">
     <cfRule type="colorScale" priority="48">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17176,12 +17697,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="containsText" dxfId="87" priority="47" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F6))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F4">
+    <cfRule type="containsText" dxfId="90" priority="47" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12">
+    <cfRule type="colorScale" priority="42">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12">
+    <cfRule type="containsText" dxfId="89" priority="41" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7">
     <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17193,12 +17731,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="containsText" dxfId="86" priority="45" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F12">
+  <conditionalFormatting sqref="F7">
+    <cfRule type="containsText" dxfId="88" priority="45" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F7))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F10">
+    <cfRule type="colorScale" priority="44">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F10">
+    <cfRule type="containsText" dxfId="87" priority="43" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F10))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14">
     <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17210,46 +17765,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F12">
-    <cfRule type="containsText" dxfId="85" priority="39" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F12))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="colorScale" priority="44">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="containsText" dxfId="84" priority="43" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F7))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F10">
-    <cfRule type="colorScale" priority="42">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F10">
-    <cfRule type="containsText" dxfId="83" priority="41" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F10))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F14">
+    <cfRule type="containsText" dxfId="86" priority="39" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F14))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15">
     <cfRule type="colorScale" priority="38">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17261,12 +17782,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F14">
-    <cfRule type="containsText" dxfId="82" priority="37" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F14))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F15">
+    <cfRule type="containsText" dxfId="85" priority="37" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F21">
     <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17278,12 +17799,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F15">
-    <cfRule type="containsText" dxfId="81" priority="35" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F21">
+    <cfRule type="containsText" dxfId="84" priority="35" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22">
     <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17295,12 +17816,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21">
-    <cfRule type="containsText" dxfId="80" priority="33" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F22">
+    <cfRule type="containsText" dxfId="83" priority="33" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F22))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23">
     <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17312,12 +17833,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F22">
-    <cfRule type="containsText" dxfId="79" priority="31" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F22))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F23">
+    <cfRule type="containsText" dxfId="82" priority="31" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F23))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F24">
     <cfRule type="colorScale" priority="30">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17329,12 +17850,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F23">
-    <cfRule type="containsText" dxfId="78" priority="29" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F23))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F24">
+    <cfRule type="containsText" dxfId="81" priority="29" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F24))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25">
     <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17346,12 +17867,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F24">
-    <cfRule type="containsText" dxfId="77" priority="27" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F24))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F25">
+    <cfRule type="containsText" dxfId="80" priority="27" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F27">
     <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17363,12 +17884,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F25">
-    <cfRule type="containsText" dxfId="76" priority="25" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F27">
+    <cfRule type="containsText" dxfId="79" priority="25" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F27))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F28">
     <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17380,12 +17901,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F27">
-    <cfRule type="containsText" dxfId="75" priority="23" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F27))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F28">
+    <cfRule type="containsText" dxfId="78" priority="23" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F28))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F29">
     <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17397,13 +17918,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F28">
-    <cfRule type="containsText" dxfId="74" priority="21" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F28))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F29">
-    <cfRule type="colorScale" priority="20">
+    <cfRule type="containsText" dxfId="77" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F26">
+    <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -17414,12 +17935,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F29">
-    <cfRule type="containsText" dxfId="73" priority="19" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F29))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F26">
+    <cfRule type="containsText" dxfId="76" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F26))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F30">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17431,12 +17952,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F26">
-    <cfRule type="containsText" dxfId="72" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F26))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F30">
+    <cfRule type="containsText" dxfId="75" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F30))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F31">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17448,12 +17969,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F30">
-    <cfRule type="containsText" dxfId="71" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F30))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F31">
+    <cfRule type="containsText" dxfId="74" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F31))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F32">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17465,12 +17986,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F31">
-    <cfRule type="containsText" dxfId="70" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F31))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F32">
+    <cfRule type="containsText" dxfId="73" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F32))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F34">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17482,12 +18003,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F32">
-    <cfRule type="containsText" dxfId="69" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F32))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F34">
+    <cfRule type="containsText" dxfId="72" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F34))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F16">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17499,12 +18020,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F34">
-    <cfRule type="containsText" dxfId="68" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F34))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F16">
+    <cfRule type="containsText" dxfId="71" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F16))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F20">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17516,12 +18037,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F16">
-    <cfRule type="containsText" dxfId="67" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F16))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F20">
+    <cfRule type="containsText" dxfId="70" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F36">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17533,9 +18054,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F20">
-    <cfRule type="containsText" dxfId="66" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
+  <conditionalFormatting sqref="F36">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F36))))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
